--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1990,27 +1990,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134082503</v>
+        <v>136161855</v>
       </c>
       <c r="B13" t="n">
-        <v>58848</v>
+        <v>57417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208242</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2023,41 +2023,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>660254</v>
+        <v>660566</v>
       </c>
       <c r="R13" t="n">
-        <v>6620560</v>
+        <v>6619885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2084,12 +2064,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,51 +2078,54 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>C260104 Odensala Harg fågelinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082503</t>
+          <t>https://artportalen.se/Sighting/136161855</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134082508</v>
+        <v>136161914</v>
       </c>
       <c r="B14" t="n">
-        <v>58848</v>
+        <v>57417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208242</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2152,44 +2135,24 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>660329</v>
+        <v>660543</v>
       </c>
       <c r="R14" t="n">
-        <v>6620899</v>
+        <v>6619907</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2216,12 +2179,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,51 +2193,54 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>C260104 Odensala Harg fågelinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082508</t>
+          <t>https://artportalen.se/Sighting/136161914</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134082509</v>
+        <v>136162209</v>
       </c>
       <c r="B15" t="n">
-        <v>58848</v>
+        <v>57417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208242</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2287,41 +2253,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>660316</v>
+        <v>660667</v>
       </c>
       <c r="R15" t="n">
-        <v>6620834</v>
+        <v>6619974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2348,12 +2294,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2362,51 +2308,54 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>C260104 Odensala Harg fågelinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082509</t>
+          <t>https://artportalen.se/Sighting/136162209</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134082510</v>
+        <v>136161849</v>
       </c>
       <c r="B16" t="n">
-        <v>58848</v>
+        <v>58550</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2416,44 +2365,24 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>660331</v>
+        <v>660637</v>
       </c>
       <c r="R16" t="n">
-        <v>6620825</v>
+        <v>6619919</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2480,12 +2409,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,51 +2423,54 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>C260104 Odensala Harg fågelinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082510</t>
+          <t>https://artportalen.se/Sighting/136161849</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134082512</v>
+        <v>136162029</v>
       </c>
       <c r="B17" t="n">
-        <v>58848</v>
+        <v>58550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208242</v>
+        <v>102990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2548,44 +2480,24 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>660329</v>
+        <v>660505</v>
       </c>
       <c r="R17" t="n">
-        <v>6620830</v>
+        <v>6619880</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2612,12 +2524,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,51 +2538,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>C260104 Odensala Harg fågelinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082512</t>
+          <t>https://artportalen.se/Sighting/136162029</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134082513</v>
+        <v>136162157</v>
       </c>
       <c r="B18" t="n">
-        <v>58848</v>
+        <v>58550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208242</v>
+        <v>102990</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2683,41 +2598,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>660304</v>
+        <v>660702</v>
       </c>
       <c r="R18" t="n">
-        <v>6620861</v>
+        <v>6619924</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2744,12 +2639,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2758,98 +2653,81 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>C260104 Odensala Harg fågelinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082513</t>
+          <t>https://artportalen.se/Sighting/136162157</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134082514</v>
+        <v>136162203</v>
       </c>
       <c r="B19" t="n">
-        <v>58848</v>
+        <v>58729</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208242</v>
+        <v>103055</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>i lekdräkt</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>660370</v>
+        <v>660700</v>
       </c>
       <c r="R19" t="n">
-        <v>6620844</v>
+        <v>6619902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2876,12 +2754,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2890,31 +2768,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>C260104 Odensala Harg fågelinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082514</t>
+          <t>https://artportalen.se/Sighting/136162203</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134082516</v>
+        <v>134082503</v>
       </c>
       <c r="B20" t="n">
         <v>58848</v>
@@ -2978,10 +2859,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>660298</v>
+        <v>660254</v>
       </c>
       <c r="R20" t="n">
-        <v>6620853</v>
+        <v>6620560</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3008,12 +2889,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3040,13 +2921,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082516</t>
+          <t>https://artportalen.se/Sighting/134082503</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134082520</v>
+        <v>134082508</v>
       </c>
       <c r="B21" t="n">
         <v>58848</v>
@@ -3076,7 +2957,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3091,12 +2972,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>i lekdräkt</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3110,10 +2991,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>660325</v>
+        <v>660329</v>
       </c>
       <c r="R21" t="n">
-        <v>6620848</v>
+        <v>6620899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3172,16 +3053,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082520</t>
+          <t>https://artportalen.se/Sighting/134082508</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135864905</v>
+        <v>134082509</v>
       </c>
       <c r="B22" t="n">
-        <v>58879</v>
+        <v>58848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,22 +3087,46 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Odensala-Harg, Upl</t>
+          <t>Odensala, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660791</v>
+        <v>660316</v>
       </c>
       <c r="R22" t="n">
-        <v>6619964</v>
+        <v>6620834</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3248,17 +3153,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>eDNA åkergroda, mindre vattensalamander, större vattensalamander. Sumpskog.</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3267,37 +3167,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Koffman, Petter Andersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
-        </is>
-      </c>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864905</t>
+          <t>https://artportalen.se/Sighting/134082509</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134137563</v>
+        <v>134082510</v>
       </c>
       <c r="B23" t="n">
-        <v>58837</v>
+        <v>58848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3305,26 +3202,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3334,11 +3231,19 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3350,10 +3255,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660121</v>
+        <v>660331</v>
       </c>
       <c r="R23" t="n">
-        <v>6620387</v>
+        <v>6620825</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3380,12 +3285,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3406,22 +3311,22 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137563</t>
+          <t>https://artportalen.se/Sighting/134082510</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134137564</v>
+        <v>134082512</v>
       </c>
       <c r="B24" t="n">
-        <v>58837</v>
+        <v>58848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,26 +3334,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3461,8 +3366,16 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3474,10 +3387,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>660197</v>
+        <v>660329</v>
       </c>
       <c r="R24" t="n">
-        <v>6620506</v>
+        <v>6620830</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3504,12 +3417,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3530,22 +3443,22 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137564</t>
+          <t>https://artportalen.se/Sighting/134082512</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134137565</v>
+        <v>134082513</v>
       </c>
       <c r="B25" t="n">
-        <v>58837</v>
+        <v>58848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3553,26 +3466,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3585,7 +3498,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>i vatten/simmande</t>
@@ -3602,10 +3519,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>660256</v>
+        <v>660304</v>
       </c>
       <c r="R25" t="n">
-        <v>6620549</v>
+        <v>6620861</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3632,17 +3549,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>10 tal grodyngel.</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3663,22 +3575,22 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137565</t>
+          <t>https://artportalen.se/Sighting/134082513</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134137567</v>
+        <v>134082514</v>
       </c>
       <c r="B26" t="n">
-        <v>58837</v>
+        <v>58848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3686,26 +3598,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3715,11 +3627,19 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3731,10 +3651,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660181</v>
+        <v>660370</v>
       </c>
       <c r="R26" t="n">
-        <v>6620382</v>
+        <v>6620844</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3761,12 +3681,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3793,16 +3713,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137567</t>
+          <t>https://artportalen.se/Sighting/134082514</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134137569</v>
+        <v>134082516</v>
       </c>
       <c r="B27" t="n">
-        <v>58837</v>
+        <v>58848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3810,21 +3730,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3837,9 +3757,21 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3851,10 +3783,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660202</v>
+        <v>660298</v>
       </c>
       <c r="R27" t="n">
-        <v>6620341</v>
+        <v>6620853</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,12 +3813,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3913,16 +3845,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137569</t>
+          <t>https://artportalen.se/Sighting/134082516</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134137576</v>
+        <v>134082520</v>
       </c>
       <c r="B28" t="n">
-        <v>58837</v>
+        <v>58848</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3930,24 +3862,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -3958,7 +3894,16 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3970,10 +3915,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660368</v>
+        <v>660325</v>
       </c>
       <c r="R28" t="n">
-        <v>6620881</v>
+        <v>6620848</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4032,16 +3977,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137576</t>
+          <t>https://artportalen.se/Sighting/134082520</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134137577</v>
+        <v>135864905</v>
       </c>
       <c r="B29" t="n">
-        <v>58837</v>
+        <v>58879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4049,50 +3994,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>660553</v>
+        <v>660791</v>
       </c>
       <c r="R29" t="n">
-        <v>6620660</v>
+        <v>6619964</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4119,12 +4053,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>eDNA åkergroda, mindre vattensalamander, större vattensalamander. Sumpskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4133,31 +4072,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Anna Koffman, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137577</t>
+          <t>https://artportalen.se/Sighting/135864905</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134137580</v>
+        <v>134137563</v>
       </c>
       <c r="B30" t="n">
         <v>58837</v>
@@ -4185,7 +4127,11 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -4197,6 +4143,7 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4208,10 +4155,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>660360</v>
+        <v>660121</v>
       </c>
       <c r="R30" t="n">
-        <v>6620839</v>
+        <v>6620387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4238,17 +4185,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Alla romklumpar uttorkade</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4269,19 +4211,19 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137580</t>
+          <t>https://artportalen.se/Sighting/134137563</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134137583</v>
+        <v>134137564</v>
       </c>
       <c r="B31" t="n">
         <v>58837</v>
@@ -4309,7 +4251,11 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -4317,10 +4263,11 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4332,10 +4279,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>660389</v>
+        <v>660197</v>
       </c>
       <c r="R31" t="n">
-        <v>6620799</v>
+        <v>6620506</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4362,12 +4309,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,19 +4335,19 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137583</t>
+          <t>https://artportalen.se/Sighting/134137564</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134137584</v>
+        <v>134137565</v>
       </c>
       <c r="B32" t="n">
         <v>58837</v>
@@ -4430,7 +4377,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4440,10 +4387,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4455,10 +4407,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>660552</v>
+        <v>660256</v>
       </c>
       <c r="R32" t="n">
-        <v>6620661</v>
+        <v>6620549</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,17 +4437,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>22 romklumpar</t>
+          <t>10 tal grodyngel.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,19 +4468,19 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137584</t>
+          <t>https://artportalen.se/Sighting/134137565</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134137585</v>
+        <v>134137567</v>
       </c>
       <c r="B33" t="n">
         <v>58837</v>
@@ -4558,7 +4510,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4572,6 +4524,7 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4583,10 +4536,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660395</v>
+        <v>660181</v>
       </c>
       <c r="R33" t="n">
-        <v>6620799</v>
+        <v>6620382</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4613,17 +4566,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>18 romklumpar</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4650,13 +4598,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137585</t>
+          <t>https://artportalen.se/Sighting/134137567</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134137586</v>
+        <v>134137569</v>
       </c>
       <c r="B34" t="n">
         <v>58837</v>
@@ -4686,7 +4634,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4694,17 +4642,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4716,10 +4656,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660390</v>
+        <v>660202</v>
       </c>
       <c r="R34" t="n">
-        <v>6620804</v>
+        <v>6620341</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4746,17 +4686,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 30 individer observerade</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4783,13 +4718,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137586</t>
+          <t>https://artportalen.se/Sighting/134137569</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134137587</v>
+        <v>134137576</v>
       </c>
       <c r="B35" t="n">
         <v>58837</v>
@@ -4825,7 +4760,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4840,10 +4775,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660360</v>
+        <v>660368</v>
       </c>
       <c r="R35" t="n">
-        <v>6620836</v>
+        <v>6620881</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4870,12 +4805,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4902,13 +4837,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137587</t>
+          <t>https://artportalen.se/Sighting/134137576</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134137590</v>
+        <v>134137577</v>
       </c>
       <c r="B36" t="n">
         <v>58837</v>
@@ -4936,11 +4871,7 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -4963,10 +4894,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660359</v>
+        <v>660553</v>
       </c>
       <c r="R36" t="n">
-        <v>6620838</v>
+        <v>6620660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4993,17 +4924,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>20 romklumpar</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5030,13 +4956,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137590</t>
+          <t>https://artportalen.se/Sighting/134137577</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134137591</v>
+        <v>134137580</v>
       </c>
       <c r="B37" t="n">
         <v>58837</v>
@@ -5064,11 +4990,7 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -5076,15 +4998,10 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5096,10 +5013,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660356</v>
+        <v>660360</v>
       </c>
       <c r="R37" t="n">
-        <v>6620844</v>
+        <v>6620839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5126,17 +5043,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst ett 30-tal individer spelandes</t>
+          <t>Alla romklumpar uttorkade</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5163,13 +5080,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137591</t>
+          <t>https://artportalen.se/Sighting/134137580</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134139010</v>
+        <v>134137583</v>
       </c>
       <c r="B38" t="n">
         <v>58837</v>
@@ -5198,13 +5115,20 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5213,10 +5137,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>660305</v>
+        <v>660389</v>
       </c>
       <c r="R38" t="n">
-        <v>6620855</v>
+        <v>6620799</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5243,12 +5167,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5275,13 +5199,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134139010</t>
+          <t>https://artportalen.se/Sighting/134137583</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134139014</v>
+        <v>134137584</v>
       </c>
       <c r="B39" t="n">
         <v>58837</v>
@@ -5309,14 +5233,25 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5325,10 +5260,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>660183</v>
+        <v>660552</v>
       </c>
       <c r="R39" t="n">
-        <v>6620394</v>
+        <v>6620661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5355,12 +5290,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>22 romklumpar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5387,13 +5327,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134139014</t>
+          <t>https://artportalen.se/Sighting/134137584</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134139017</v>
+        <v>134137585</v>
       </c>
       <c r="B40" t="n">
         <v>58837</v>
@@ -5421,14 +5361,25 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5437,10 +5388,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>660238</v>
+        <v>660395</v>
       </c>
       <c r="R40" t="n">
-        <v>6620550</v>
+        <v>6620799</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5467,12 +5418,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>18 romklumpar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5499,16 +5455,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134139017</t>
+          <t>https://artportalen.se/Sighting/134137585</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135864906</v>
+        <v>134137586</v>
       </c>
       <c r="B41" t="n">
-        <v>58868</v>
+        <v>58837</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5533,22 +5489,42 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Odensala-Harg, Upl</t>
+          <t>Odensala, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>660791</v>
+        <v>660390</v>
       </c>
       <c r="R41" t="n">
-        <v>6619964</v>
+        <v>6620804</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5575,17 +5551,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>eDNA åkergroda, mindre vattensalamander, större vattensalamander. Sumpskog.</t>
+          <t>Minst 30 individer observerade</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5594,37 +5570,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Koffman, Petter Andersson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
-        </is>
-      </c>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135864906</t>
+          <t>https://artportalen.se/Sighting/134137586</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135864917</v>
+        <v>134137587</v>
       </c>
       <c r="B42" t="n">
-        <v>58868</v>
+        <v>58837</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5649,26 +5622,33 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Odensala-Harg, Upl</t>
+          <t>Odensala, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>660652</v>
+        <v>660360</v>
       </c>
       <c r="R42" t="n">
-        <v>6619909</v>
+        <v>6620836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5695,17 +5675,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Subadult, I vatten/simmandefylld körskada</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5714,26 +5689,856 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137587</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134137590</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>660359</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6620838</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20 romklumpar</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137590</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134137591</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>660356</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6620844</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst ett 30-tal individer spelandes</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137591</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134139010</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>660305</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6620855</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139010</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134139014</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>660183</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6620394</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139014</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134139017</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>660238</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6620550</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139017</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135864906</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58868</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Odensala-Harg, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>660791</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6619964</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>eDNA åkergroda, mindre vattensalamander, större vattensalamander. Sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
           <t>Marlijn Sterenborg</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anna Koffman, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864906</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135864917</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58868</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Odensala-Harg, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>660652</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6619909</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Subadult, I vatten/simmandefylld körskada</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Petter Andersson</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
+      <c r="AY49" t="inlineStr">
         <is>
           <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135864917</t>
         </is>
@@ -5782,6 +6587,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1993,7 +1993,7 @@
         <v>136161855</v>
       </c>
       <c r="B13" t="n">
-        <v>57417</v>
+        <v>57419</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136161914</v>
       </c>
       <c r="B14" t="n">
-        <v>57417</v>
+        <v>57419</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136162209</v>
       </c>
       <c r="B15" t="n">
-        <v>57417</v>
+        <v>57419</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>136161849</v>
       </c>
       <c r="B16" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>136162029</v>
       </c>
       <c r="B17" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136162157</v>
       </c>
       <c r="B18" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>136162203</v>
       </c>
       <c r="B19" t="n">
-        <v>58729</v>
+        <v>58731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
